--- a/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>13.8</v>
       </c>
     </row>
     <row r="14" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -568,7 +568,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>15.2</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>14.6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>15.5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -819,8 +819,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31">
-        <v>14.2</v>
+      <c r="D31" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:4">
